--- a/data/trending_integrated_20261030_12.xlsx
+++ b/data/trending_integrated_20261030_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23100</v>
+        <v>24200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+156.67%</t>
+          <t>'+168.89%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>447</v>
+        <v>511</v>
       </c>
       <c r="F2" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="G2" t="n">
-        <v>531</v>
+        <v>599</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -601,7 +601,7 @@
         <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>23350</v>
+        <v>24950</v>
       </c>
       <c r="M2" t="n">
         <v>16450</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>426587473790</v>
+        <v>474069468815</v>
       </c>
       <c r="P2" t="n">
-        <v>23350</v>
+        <v>24950</v>
       </c>
       <c r="Q2" t="n">
         <v>16450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장 후 급등락 반복. 단기 차익 실현 및 기술적 분석 기반의 매매 관점.</t>
+          <t>신규 상장주로서의 변동성. 26년 IPO 대장 기대감 및 K-팔란티어 언급. 개인 투자자들의 관심.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장', '단타', '기술적 분석']</t>
+          <t>['신규 상장주', 'IPO', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19300</v>
+        <v>19220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.92%</t>
+          <t>'+15.44%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -702,7 +702,7 @@
         <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>97587508225</v>
+        <v>99374456100</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자 보안 관련 법 시행 및 해킹 사태로 인한 수혜 기대감. 보안 대장주로서의 상승 가능성 부각.</t>
+          <t>양자 관련 법 시행 수혜 및 보안 대장주로서의 기대감. 바이낸스, 빗썸 해킹 사태 반사이익 전망. 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '보안주']</t>
+          <t>['양자보안', '해킹', '수혜주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8810</v>
+        <v>2820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.42%</t>
+          <t>'+15.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
-        <v>13.29</v>
+        <v>0.79</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7700</v>
+        <v>2450</v>
       </c>
       <c r="K4" t="n">
-        <v>9360</v>
+        <v>2460</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>3110</v>
       </c>
       <c r="M4" t="n">
-        <v>8430</v>
+        <v>2335</v>
       </c>
       <c r="N4" t="n">
-        <v>12.92</v>
+        <v>0.63</v>
       </c>
       <c r="O4" t="n">
-        <v>7446335745</v>
+        <v>11906171263</v>
       </c>
       <c r="P4" t="n">
-        <v>13670</v>
+        <v>3170</v>
       </c>
       <c r="Q4" t="n">
-        <v>7060</v>
+        <v>880</v>
       </c>
       <c r="R4" t="n">
-        <v>-25000</v>
+        <v>-14000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['임상 3상', '위식도염', '시장 규모']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2790</v>
+        <v>7040</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.88%</t>
+          <t>'+12.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="H5" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2450</v>
+        <v>6240</v>
       </c>
       <c r="K5" t="n">
-        <v>2460</v>
+        <v>6700</v>
       </c>
       <c r="L5" t="n">
-        <v>3110</v>
+        <v>7670</v>
       </c>
       <c r="M5" t="n">
-        <v>2335</v>
+        <v>6330</v>
       </c>
       <c r="N5" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>11725713574</v>
+        <v>17372341220</v>
       </c>
       <c r="P5" t="n">
-        <v>3170</v>
+        <v>16620</v>
       </c>
       <c r="Q5" t="n">
-        <v>880</v>
+        <v>4600</v>
       </c>
       <c r="R5" t="n">
-        <v>-14000</v>
+        <v>9000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>건설 경기 전환점 및 재료 기반 상승 기대. 유상 청약율 및 시장 상황 고려 필요.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['건설 경기', '유상 청약', '재료']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12310</v>
+        <v>8590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.91%</t>
+          <t>'+11.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>256</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>751</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
-        <v>15.04</v>
+        <v>13.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11200</v>
+        <v>7700</v>
       </c>
       <c r="K6" t="n">
-        <v>13500</v>
+        <v>9360</v>
       </c>
       <c r="L6" t="n">
-        <v>13710</v>
+        <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>12100</v>
+        <v>8430</v>
       </c>
       <c r="N6" t="n">
-        <v>15.08</v>
+        <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>41970895065</v>
+        <v>7915161860</v>
       </c>
       <c r="P6" t="n">
-        <v>18960</v>
+        <v>13670</v>
       </c>
       <c r="Q6" t="n">
-        <v>5730</v>
+        <v>7060</v>
       </c>
       <c r="R6" t="n">
-        <v>-275000</v>
+        <v>-25000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 시장 석권 기대. 기술 개발 관련 긍정적 평가 및 저가 매수 기회 언급.</t>
+          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '시장 석권']</t>
+          <t>['임상 3상', '위식도염', '시장 규모']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6660</v>
+        <v>12040</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.73%</t>
+          <t>'+7.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>261</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="G7" t="n">
-        <v>136</v>
+        <v>760</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>15.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6240</v>
+        <v>11200</v>
       </c>
       <c r="K7" t="n">
-        <v>6700</v>
+        <v>13500</v>
       </c>
       <c r="L7" t="n">
-        <v>7670</v>
+        <v>13710</v>
       </c>
       <c r="M7" t="n">
-        <v>6330</v>
+        <v>12000</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>16140713195</v>
+        <v>44139420335</v>
       </c>
       <c r="P7" t="n">
-        <v>16620</v>
+        <v>18960</v>
       </c>
       <c r="Q7" t="n">
-        <v>4600</v>
+        <v>5730</v>
       </c>
       <c r="R7" t="n">
-        <v>9000</v>
+        <v>-275000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>건설 경기 전환점 및 재료 기반 상승 기대. 유상 청약율 및 시장 상황 고려 필요.</t>
+          <t>희토류 없는 백색 LED 세계 최초 개발 및 언론 보도. 100억 달러 시장 석권 기대감. 주당 10만원 이상 목표.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['건설 경기', '유상 청약', '재료']</t>
+          <t>['백색 LED', '희토류', '시장 석권']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29050</v>
+        <v>15490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.57%</t>
+          <t>'+3.40%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>272</v>
+        <v>338</v>
       </c>
       <c r="H8" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K8" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L8" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M8" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>108582762150</v>
+        <v>43990013620</v>
       </c>
       <c r="P8" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>-45000</v>
+        <v>109000</v>
       </c>
       <c r="S8" t="n">
-        <v>95000</v>
+        <v>168000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15460</v>
+        <v>29000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.20%</t>
+          <t>'+3.39%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>341</v>
+        <v>274</v>
       </c>
       <c r="H9" t="n">
-        <v>7.15</v>
+        <v>4.69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>28050</v>
       </c>
       <c r="K9" t="n">
-        <v>14980</v>
+        <v>27850</v>
       </c>
       <c r="L9" t="n">
-        <v>16150</v>
+        <v>30400</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>27650</v>
       </c>
       <c r="N9" t="n">
-        <v>8.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>43412128815</v>
+        <v>109842107850</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>50600</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>13210</v>
       </c>
       <c r="R9" t="n">
-        <v>109000</v>
+        <v>-45000</v>
       </c>
       <c r="S9" t="n">
-        <v>168000</v>
+        <v>95000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50500</v>
+        <v>50100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.85%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H10" t="n">
         <v>23.82</v>
@@ -1346,7 +1346,7 @@
         <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>49298801125</v>
+        <v>49773608075</v>
       </c>
       <c r="P10" t="n">
         <v>97900</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15790</v>
+        <v>15760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
         <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>38755378765</v>
+        <v>39337297495</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6620</v>
+        <v>6640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
         <v>0.85</v>
@@ -1530,7 +1530,7 @@
         <v>0.9</v>
       </c>
       <c r="O12" t="n">
-        <v>30272897685</v>
+        <v>30351110075</v>
       </c>
       <c r="P12" t="n">
         <v>9820</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7300</v>
+        <v>7270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H13" t="n">
         <v>25.3</v>
@@ -1616,13 +1616,13 @@
         <v>7570</v>
       </c>
       <c r="M13" t="n">
-        <v>7280</v>
+        <v>7270</v>
       </c>
       <c r="N13" t="n">
         <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>7678019245</v>
+        <v>7912741420</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61400</v>
+        <v>61200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.23%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H14" t="n">
         <v>41.76</v>
@@ -1714,7 +1714,7 @@
         <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>68028380900</v>
+        <v>69534911100</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3940</v>
+        <v>3900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-3.47%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.77</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H15" t="n">
         <v>1.43</v>
@@ -1806,7 +1806,7 @@
         <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>73291301703</v>
+        <v>74822797414</v>
       </c>
       <c r="P15" t="n">
         <v>8100</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8300</v>
+        <v>8270</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.26%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H16" t="n">
         <v>2.67</v>
@@ -1892,13 +1892,13 @@
         <v>11150</v>
       </c>
       <c r="M16" t="n">
-        <v>8300</v>
+        <v>8110</v>
       </c>
       <c r="N16" t="n">
         <v>2.66</v>
       </c>
       <c r="O16" t="n">
-        <v>26764409640</v>
+        <v>27285590410</v>
       </c>
       <c r="P16" t="n">
         <v>19270</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54000</v>
+        <v>53800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.76%</t>
+          <t>'-5.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F17" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G17" t="n">
-        <v>908</v>
+        <v>928</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>66819395300</v>
+        <v>68100841800</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 SMR 원자로 수주 및 실적 호조에도 불구하고 주가 부진. 정부 정책 및 금융 시장 불안정성이 투자 심리 악화.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 그러나 금융시장 무정부 상태 및 무능 정권 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '실적']</t>
+          <t>['SMR', '원자로 수주', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10950</v>
+        <v>10920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.77%</t>
+          <t>'-6.02%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F18" t="n">
         <v>163</v>
       </c>
       <c r="G18" t="n">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2076,13 +2076,13 @@
         <v>11470</v>
       </c>
       <c r="M18" t="n">
-        <v>10920</v>
+        <v>10910</v>
       </c>
       <c r="N18" t="n">
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>44456620860</v>
+        <v>45502317195</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>217750</v>
+        <v>217500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.14%</t>
+          <t>'-6.25%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G19" t="n">
-        <v>1383</v>
+        <v>1428</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>2051713523000</v>
+        <v>2098147042500</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 주가 하락 우려 제기. 일부 투자자는 주주 환원 발표를 기다리며 가격 반등을 기대.</t>
+          <t>이재용 상속세, 무능 정부, 외인 매수 부재 등으로 인한 주가 하락 우려. 주주환원 기대감 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상속세', '주주환원', '코스피']</t>
+          <t>['상속세', '주주환원']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22000</v>
+        <v>21950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.78%</t>
+          <t>'-6.99%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.63</v>
       </c>
       <c r="E20" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F20" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G20" t="n">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="H20" t="n">
         <v>11.6</v>
@@ -2266,7 +2266,7 @@
         <v>12.23</v>
       </c>
       <c r="O20" t="n">
-        <v>70390039900</v>
+        <v>71152533300</v>
       </c>
       <c r="P20" t="n">
         <v>59300</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>김동원 부회장 주가 누르기 의혹과 함께 급락세 지속. 태양광 사업 호재에도 불구하고 주가 부양책 부재에 대한 불만.</t>
+          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 사업 관련 긍정적 뉴스(RE100, 물량 완판)에도 불구하고 급락세 지속.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['태양광', '주가 누르기', 'RE100']</t>
+          <t>['주가 누르기', '태양광', 'RE100']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>170100</v>
+        <v>169900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.50%</t>
+          <t>'-7.61%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="H21" t="n">
         <v>74.87</v>
@@ -2358,7 +2358,7 @@
         <v>75</v>
       </c>
       <c r="O21" t="n">
-        <v>478258030850</v>
+        <v>490363644400</v>
       </c>
       <c r="P21" t="n">
         <v>243500</v>
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13750</v>
+        <v>1390000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.52%</t>
+          <t>'-8.91%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E22" t="n">
-        <v>105</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>56</v>
+        <v>529</v>
       </c>
       <c r="G22" t="n">
-        <v>377</v>
+        <v>1317</v>
       </c>
       <c r="H22" t="n">
-        <v>3.13</v>
+        <v>48.72</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>15030</v>
+        <v>1526000</v>
       </c>
       <c r="K22" t="n">
-        <v>14500</v>
+        <v>1444000</v>
       </c>
       <c r="L22" t="n">
-        <v>14570</v>
+        <v>1446000</v>
       </c>
       <c r="M22" t="n">
-        <v>13710</v>
+        <v>1381000</v>
       </c>
       <c r="N22" t="n">
-        <v>3.33</v>
+        <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>38455702385</v>
+        <v>2575889582000</v>
       </c>
       <c r="P22" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>1830</v>
+        <v>501000</v>
       </c>
       <c r="R22" t="n">
-        <v>-118000</v>
+        <v>-165000</v>
       </c>
       <c r="S22" t="n">
-        <v>-23000</v>
+        <v>-76000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>대규모 하락장 속에서 광통신 주식에 대한 투자 심리 위축. 3만 전고점까지 보유 의견 존재.</t>
+          <t>증시 전반의 급락 속 SK하이닉스 주가 하락. 엔비디아 회복세에도 불구하고 개인 투자자들의 대량 매수세 유입.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['광통신', '하락장', '전고점']</t>
+          <t>['증시 급락', '엔비디아', '개인 매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1391000</v>
+        <v>13680</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.85%</t>
+          <t>'-8.98%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>106</v>
       </c>
       <c r="F23" t="n">
-        <v>523</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
-        <v>1336</v>
+        <v>382</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72</v>
+        <v>3.13</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1526000</v>
+        <v>15030</v>
       </c>
       <c r="K23" t="n">
-        <v>1444000</v>
+        <v>14500</v>
       </c>
       <c r="L23" t="n">
-        <v>1446000</v>
+        <v>14570</v>
       </c>
       <c r="M23" t="n">
-        <v>1381000</v>
+        <v>13680</v>
       </c>
       <c r="N23" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>2529998152000</v>
+        <v>39356518635</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>501000</v>
+        <v>1830</v>
       </c>
       <c r="R23" t="n">
-        <v>-165000</v>
+        <v>-118000</v>
       </c>
       <c r="S23" t="n">
-        <v>-76000</v>
+        <v>-23000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>코스피 급락 속 SK하이닉스 주가 하락 심화. 정부 정책 및 해외 증시 영향으로 투자 심리 위축.</t>
+          <t>광통신 섹터 내에서의 기대감. 루멘텀 홀딩스 관련 호재에도 불구하고 한국장 불신으로 인한 하락. 오후 반등 예상.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['코스피', '엔비디아', 'PER']</t>
+          <t>['광통신', '루멘텀', '호재']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7140</v>
+        <v>7170</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.62%</t>
+          <t>'-9.24%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2628,13 +2628,13 @@
         <v>8130</v>
       </c>
       <c r="M24" t="n">
-        <v>7100</v>
+        <v>7050</v>
       </c>
       <c r="N24" t="n">
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>14676033580</v>
+        <v>15039184720</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116200</v>
+        <v>115300</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.92%</t>
+          <t>'-16.57%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F25" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G25" t="n">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2720,13 +2720,13 @@
         <v>132900</v>
       </c>
       <c r="M25" t="n">
-        <v>116100</v>
+        <v>115200</v>
       </c>
       <c r="N25" t="n">
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>125242139900</v>
+        <v>129870458350</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 발표 전 급락세 지속. SK하이닉스 물량 확대 및 기판주 대표로서의 하락 압력.</t>
+          <t>실적 기대감 대비 큰 폭의 하락세. 기관의 매도세와 함께 '수작' 의혹 제기.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['기판주', '실적', 'SK하이닉스']</t>
+          <t>['실적', '기관 매도', '하락']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13190</v>
+        <v>13040</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-22.41%</t>
+          <t>'-23.29%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G26" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2812,13 +2812,13 @@
         <v>14900</v>
       </c>
       <c r="M26" t="n">
-        <v>13080</v>
+        <v>13000</v>
       </c>
       <c r="N26" t="n">
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>30553332565</v>
+        <v>31356389245</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>마이크론 퀄테스트 통과 및 장비 수주 공시 기대. 보호예수 물량 출회로 인한 급락세 지속 및 저가 매수 기회 언급.</t>
+          <t>보호예수 물량 매도와 반도체 업황 부진으로 급락했으나, 마이크론 퀄테스트 통과 소식과 ASML 장비 수주 공시 기대감으로 저가 매수 기회라는 분석.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['마이크론', '퀄테스트', '보호예수']</t>
+          <t>['보호예수', '퀄테스트', '장비수주']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2863,79 +2863,79 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>벡트로보틱스</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10700</v>
+        <v>1829</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.67%</t>
+          <t>'-28.97%</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E27" t="n">
+        <v>75</v>
+      </c>
+      <c r="F27" t="n">
+        <v>43</v>
+      </c>
+      <c r="G27" t="n">
+        <v>44</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7202776610</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R27" t="n">
+        <v>73000</v>
+      </c>
+      <c r="S27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>333</v>
-      </c>
-      <c r="F27" t="n">
-        <v>162</v>
-      </c>
-      <c r="G27" t="n">
-        <v>596</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L27" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M27" t="n">
-        <v>9790</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>101819827740</v>
-      </c>
-      <c r="P27" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>9790</v>
-      </c>
-      <c r="R27" t="n">
-        <v>-41000</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-216000</v>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>상장 직후 급락 후 반등 시도. 높은 당기순이익 및 매출, 영업이익 수치 제시. 기관 물량 소화 후 상승 기대.</t>
+          <t>연이은 하한가 기록. 투자자 불안감 고조 및 상장폐지 우려 제기.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상장', '반등', '기관 물량']</t>
+          <t>['하한가', '유상증자', '상장폐지']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2943,43 +2943,43 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>439270</t>
+          <t>457600</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>벡트로보틱스</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1819</v>
+        <v>10420</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-29.36%</t>
+          <t>'-30.53%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>69</v>
+        <v>358</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="G28" t="n">
-        <v>34</v>
+        <v>615</v>
       </c>
       <c r="H28" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,47 +2987,47 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>2575</v>
+        <v>15000</v>
       </c>
       <c r="K28" t="n">
-        <v>1960</v>
+        <v>12000</v>
       </c>
       <c r="L28" t="n">
-        <v>2005</v>
+        <v>12700</v>
       </c>
       <c r="M28" t="n">
-        <v>1805</v>
+        <v>9790</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>7104603205</v>
+        <v>104086434110</v>
       </c>
       <c r="P28" t="n">
-        <v>5700</v>
+        <v>12700</v>
       </c>
       <c r="Q28" t="n">
-        <v>1401</v>
+        <v>9790</v>
       </c>
       <c r="R28" t="n">
-        <v>73000</v>
+        <v>-41000</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-216000</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>연이은 하한가 기록. 투자자 불안감 고조 및 상장폐지 우려 제기.</t>
+          <t>상장 직후 급락 후 반등 시도. 당기순이익 및 매출액 호조. 실내골프대회 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['하한가', '유상증자', '상장폐지']</t>
+          <t>['당기순이익', '매출', '실내골프']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>457600</t>
+          <t>439270</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261030_12.xlsx
+++ b/data/trending_integrated_20261030_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24200</v>
+        <v>26450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+168.89%</t>
+          <t>'+193.89%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>511</v>
+        <v>600</v>
       </c>
       <c r="F2" t="n">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="G2" t="n">
-        <v>599</v>
+        <v>679</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -601,7 +601,7 @@
         <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>24950</v>
+        <v>27000</v>
       </c>
       <c r="M2" t="n">
         <v>16450</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>474069468815</v>
+        <v>534735890615</v>
       </c>
       <c r="P2" t="n">
-        <v>24950</v>
+        <v>27000</v>
       </c>
       <c r="Q2" t="n">
         <v>16450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주로서의 변동성. 26년 IPO 대장 기대감 및 K-팔란티어 언급. 개인 투자자들의 관심.</t>
+          <t>신규 상장주의 높은 변동성과 급락에 대한 우려 속에서도 목표가 제시 및 상승 가능성에 대한 기대감이 일부 존재함. 엔비디아 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장주', 'IPO', '변동성']</t>
+          <t>['신규상장주', '목표가', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19220</v>
+        <v>7150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.44%</t>
+          <t>'+14.58%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,222 +687,222 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16650</v>
+        <v>6240</v>
       </c>
       <c r="K3" t="n">
-        <v>16830</v>
+        <v>6700</v>
       </c>
       <c r="L3" t="n">
-        <v>19750</v>
+        <v>7670</v>
       </c>
       <c r="M3" t="n">
-        <v>16750</v>
+        <v>6330</v>
       </c>
       <c r="N3" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>99374456100</v>
+        <v>19004009375</v>
       </c>
       <c r="P3" t="n">
-        <v>22450</v>
+        <v>16620</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>4600</v>
       </c>
       <c r="R3" t="n">
-        <v>94000</v>
+        <v>9000</v>
       </c>
       <c r="S3" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자 관련 법 시행 수혜 및 보안 대장주로서의 기대감. 바이낸스, 빗썸 해킹 사태 반사이익 전망. 프로그램 매수세 유입.</t>
+          <t>건설 경기 전환점 및 재료 기반 상승 기대. 유상 청약율 및 시장 상황 고려 필요.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '수혜주']</t>
+          <t>['건설 경기', '유상 청약', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2820</v>
+        <v>18980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.10%</t>
+          <t>'+13.99%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.16</v>
+        <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H4" t="n">
-        <v>0.79</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2450</v>
+        <v>16650</v>
       </c>
       <c r="K4" t="n">
-        <v>2460</v>
+        <v>16830</v>
       </c>
       <c r="L4" t="n">
-        <v>3110</v>
+        <v>19750</v>
       </c>
       <c r="M4" t="n">
-        <v>2335</v>
+        <v>16750</v>
       </c>
       <c r="N4" t="n">
-        <v>0.63</v>
+        <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>11906171263</v>
+        <v>101379855520</v>
       </c>
       <c r="P4" t="n">
-        <v>3170</v>
+        <v>22450</v>
       </c>
       <c r="Q4" t="n">
-        <v>880</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-14000</v>
+        <v>94000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>양자 관련 법 시행 수혜 및 보안 대장주로서의 기대감. 바이낸스, 빗썸 해킹 사태 반사이익 전망. 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['양자보안', '해킹', '수혜주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7040</v>
+        <v>2750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.82%</t>
+          <t>'+12.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6240</v>
+        <v>2450</v>
       </c>
       <c r="K5" t="n">
-        <v>6700</v>
+        <v>2460</v>
       </c>
       <c r="L5" t="n">
-        <v>7670</v>
+        <v>3110</v>
       </c>
       <c r="M5" t="n">
-        <v>6330</v>
+        <v>2335</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>17372341220</v>
+        <v>12033885513</v>
       </c>
       <c r="P5" t="n">
-        <v>16620</v>
+        <v>3170</v>
       </c>
       <c r="Q5" t="n">
-        <v>4600</v>
+        <v>880</v>
       </c>
       <c r="R5" t="n">
-        <v>9000</v>
+        <v>-14000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>건설 경기 전환점 및 재료 기반 상승 기대. 유상 청약율 및 시장 상황 고려 필요.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['건설 경기', '유상 청약', '재료']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8590</v>
+        <v>8580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.56%</t>
+          <t>'+11.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
         <v>38</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>7915161860</v>
+        <v>8006784560</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12040</v>
+        <v>12110</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.50%</t>
+          <t>'+8.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="F7" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G7" t="n">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1064,13 +1064,13 @@
         <v>13710</v>
       </c>
       <c r="M7" t="n">
-        <v>12000</v>
+        <v>11750</v>
       </c>
       <c r="N7" t="n">
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>44139420335</v>
+        <v>46556179580</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15490</v>
+        <v>15550</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.40%</t>
+          <t>'+3.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H8" t="n">
         <v>7.15</v>
@@ -1162,7 +1162,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>43990013620</v>
+        <v>44306331845</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1222,13 +1222,13 @@
         <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="H9" t="n">
         <v>4.69</v>
@@ -1254,7 +1254,7 @@
         <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>109842107850</v>
+        <v>111771814350</v>
       </c>
       <c r="P9" t="n">
         <v>50600</v>
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50100</v>
+        <v>50300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.04%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
         <v>60</v>
@@ -1346,7 +1346,7 @@
         <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>49773608075</v>
+        <v>50268939900</v>
       </c>
       <c r="P10" t="n">
         <v>97900</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15760</v>
+        <v>15800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+0.51%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>39337297495</v>
+        <v>40396895895</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 조선주 강세와 대비되는 국내 조선주 약세. 실적 서프라이즈 및 증권사 리포트 긍정 전망에도 불구하고 업황 둔화 우려.</t>
+          <t>미국 조선주 강세 속에서 국내 조선주 기회론이 제기되었으나, 업황 둔화 및 승계 이슈에 대한 우려도 존재함. 리포트 쏟아짐.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '실적 서프라이즈', '업황']</t>
+          <t>['조선주', '호재', '업황']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6640</v>
+        <v>6590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1530,7 +1530,7 @@
         <v>0.9</v>
       </c>
       <c r="O12" t="n">
-        <v>30351110075</v>
+        <v>30521364695</v>
       </c>
       <c r="P12" t="n">
         <v>9820</v>
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7270</v>
+        <v>3950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>-0.77</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="H13" t="n">
-        <v>25.3</v>
+        <v>1.43</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7450</v>
+        <v>4040</v>
       </c>
       <c r="K13" t="n">
-        <v>7350</v>
+        <v>3925</v>
       </c>
       <c r="L13" t="n">
-        <v>7570</v>
+        <v>4265</v>
       </c>
       <c r="M13" t="n">
-        <v>7270</v>
+        <v>3880</v>
       </c>
       <c r="N13" t="n">
-        <v>25.32</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>7912741420</v>
+        <v>75602408845</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>7010</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>95000</v>
+        <v>-37000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['급등 기대', '외국인 매수', '개잡주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61200</v>
+        <v>7270</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
-        <v>274</v>
+        <v>191</v>
       </c>
       <c r="H14" t="n">
-        <v>41.76</v>
+        <v>25.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62800</v>
+        <v>7450</v>
       </c>
       <c r="K14" t="n">
-        <v>62300</v>
+        <v>7350</v>
       </c>
       <c r="L14" t="n">
-        <v>62800</v>
+        <v>7570</v>
       </c>
       <c r="M14" t="n">
-        <v>60700</v>
+        <v>7250</v>
       </c>
       <c r="N14" t="n">
-        <v>41.55</v>
+        <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>69534911100</v>
+        <v>8186060085</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>7010</v>
       </c>
       <c r="R14" t="n">
-        <v>117000</v>
+        <v>95000</v>
       </c>
       <c r="S14" t="n">
-        <v>-38000</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3900</v>
+        <v>61200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>171</v>
+        <v>283</v>
       </c>
       <c r="H15" t="n">
-        <v>1.43</v>
+        <v>41.76</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4040</v>
+        <v>62800</v>
       </c>
       <c r="K15" t="n">
-        <v>3925</v>
+        <v>62300</v>
       </c>
       <c r="L15" t="n">
-        <v>4265</v>
+        <v>62800</v>
       </c>
       <c r="M15" t="n">
-        <v>3880</v>
+        <v>60700</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>41.55</v>
       </c>
       <c r="O15" t="n">
-        <v>74822797414</v>
+        <v>71544465400</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>-37000</v>
+        <v>117000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-38000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['급등 기대', '외국인 매수', '개잡주']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8270</v>
+        <v>8230</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-4.08%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
         <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H16" t="n">
         <v>2.67</v>
@@ -1898,7 +1898,7 @@
         <v>2.66</v>
       </c>
       <c r="O16" t="n">
-        <v>27285590410</v>
+        <v>27648065560</v>
       </c>
       <c r="P16" t="n">
         <v>19270</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53800</v>
+        <v>54000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.11%</t>
+          <t>'-4.76%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="F17" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G17" t="n">
-        <v>928</v>
+        <v>958</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1984,13 +1984,13 @@
         <v>55900</v>
       </c>
       <c r="M17" t="n">
-        <v>53800</v>
+        <v>53700</v>
       </c>
       <c r="N17" t="n">
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>68100841800</v>
+        <v>70140133950</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10920</v>
+        <v>218500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.02%</t>
+          <t>'-5.82%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>163</v>
+        <v>564</v>
       </c>
       <c r="G18" t="n">
-        <v>1094</v>
+        <v>1487</v>
       </c>
       <c r="H18" t="n">
-        <v>9.73</v>
+        <v>46.17</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>11620</v>
+        <v>232000</v>
       </c>
       <c r="K18" t="n">
-        <v>11300</v>
+        <v>223500</v>
       </c>
       <c r="L18" t="n">
-        <v>11470</v>
+        <v>229500</v>
       </c>
       <c r="M18" t="n">
-        <v>10910</v>
+        <v>216500</v>
       </c>
       <c r="N18" t="n">
-        <v>9.6</v>
+        <v>46.19</v>
       </c>
       <c r="O18" t="n">
-        <v>45502317195</v>
+        <v>2151855308500</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R18" t="n">
-        <v>-213000</v>
+        <v>951000</v>
       </c>
       <c r="S18" t="n">
-        <v>-60000</v>
+        <v>-298000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>가덕도 공사비 증액 및 재건 사업 기대감. 공매도 금지 조치에 따른 영향 분석.</t>
+          <t>이재용 상속세 관련 정치적 언급과 함께 국장 전반의 하락세 및 삼성전자 주가에 대한 부정적 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['가덕도', '공사비', '재건']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>217500</v>
+        <v>10940</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.25%</t>
+          <t>'-5.85%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>356</v>
       </c>
       <c r="F19" t="n">
-        <v>565</v>
+        <v>164</v>
       </c>
       <c r="G19" t="n">
-        <v>1428</v>
+        <v>1104</v>
       </c>
       <c r="H19" t="n">
-        <v>46.17</v>
+        <v>9.73</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>232000</v>
+        <v>11620</v>
       </c>
       <c r="K19" t="n">
-        <v>223500</v>
+        <v>11300</v>
       </c>
       <c r="L19" t="n">
-        <v>229500</v>
+        <v>11470</v>
       </c>
       <c r="M19" t="n">
-        <v>216500</v>
+        <v>10890</v>
       </c>
       <c r="N19" t="n">
-        <v>46.19</v>
+        <v>9.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2098147042500</v>
+        <v>46952213880</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>951000</v>
+        <v>-213000</v>
       </c>
       <c r="S19" t="n">
-        <v>-298000</v>
+        <v>-60000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>이재용 상속세, 무능 정부, 외인 매수 부재 등으로 인한 주가 하락 우려. 주주환원 기대감 존재.</t>
+          <t>가덕도 공사비 증액 및 재건 사업 기대감. 공매도 금지 조치에 따른 영향 분석.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상속세', '주주환원']</t>
+          <t>['가덕도', '공사비', '재건']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21950</v>
+        <v>22000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.99%</t>
+          <t>'-6.78%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.63</v>
       </c>
       <c r="E20" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F20" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G20" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="H20" t="n">
         <v>11.6</v>
@@ -2266,7 +2266,7 @@
         <v>12.23</v>
       </c>
       <c r="O20" t="n">
-        <v>71152533300</v>
+        <v>72162976275</v>
       </c>
       <c r="P20" t="n">
         <v>59300</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>169900</v>
+        <v>170700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.61%</t>
+          <t>'-7.18%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H21" t="n">
         <v>74.87</v>
@@ -2358,7 +2358,7 @@
         <v>75</v>
       </c>
       <c r="O21" t="n">
-        <v>490363644400</v>
+        <v>500157193250</v>
       </c>
       <c r="P21" t="n">
         <v>243500</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1390000</v>
+        <v>1398000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.91%</t>
+          <t>'-8.39%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>529</v>
       </c>
       <c r="G22" t="n">
-        <v>1317</v>
+        <v>1300</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>2575889582000</v>
+        <v>2632695966000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>증시 전반의 급락 속 SK하이닉스 주가 하락. 엔비디아 회복세에도 불구하고 개인 투자자들의 대량 매수세 유입.</t>
+          <t>증시 폭락 속에서 SK하이닉스 주가 하락에 대한 불만과 함께 정치적 책임론이 제기되었으며, 향후 주가에 대한 부정적 전망이 지배적임.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['증시 급락', '엔비디아', '개인 매수']</t>
+          <t>['폭락', '정권', '증시']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13680</v>
+        <v>13710</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.98%</t>
+          <t>'-8.78%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F23" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2536,13 +2536,13 @@
         <v>14570</v>
       </c>
       <c r="M23" t="n">
-        <v>13680</v>
+        <v>13590</v>
       </c>
       <c r="N23" t="n">
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>39356518635</v>
+        <v>40738179815</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7170</v>
+        <v>7100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.24%</t>
+          <t>'-10.13%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>15039184720</v>
+        <v>15177483110</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>115300</v>
+        <v>116100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-16.57%</t>
+          <t>'-15.99%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F25" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2720,13 +2720,13 @@
         <v>132900</v>
       </c>
       <c r="M25" t="n">
-        <v>115200</v>
+        <v>114300</v>
       </c>
       <c r="N25" t="n">
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>129870458350</v>
+        <v>137263452500</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 기대감 대비 큰 폭의 하락세. 기관의 매도세와 함께 '수작' 의혹 제기.</t>
+          <t>급격한 주가 하락에 대한 의문과 함께 실적 호조에도 불구하고 하락하는 시장 상황에 대한 불만이 표출됨. 기관 및 외국인 매도세에 대한 비판도 제기됨.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '기관 매도', '하락']</t>
+          <t>['실적', '하락', '기관']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13040</v>
+        <v>13130</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-23.29%</t>
+          <t>'-22.76%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F26" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G26" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2812,13 +2812,13 @@
         <v>14900</v>
       </c>
       <c r="M26" t="n">
-        <v>13000</v>
+        <v>12930</v>
       </c>
       <c r="N26" t="n">
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>31356389245</v>
+        <v>32166881345</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 매도와 반도체 업황 부진으로 급락했으나, 마이크론 퀄테스트 통과 소식과 ASML 장비 수주 공시 기대감으로 저가 매수 기회라는 분석.</t>
+          <t>보호예수 물량 출회 및 급락하는 시장 상황 속에서 주가 하락에 대한 불만이 제기되었으나, 마이크론 퀄테스트 통과 및 장비 수주 공시 기대감이 언급됨.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '퀄테스트', '장비수주']</t>
+          <t>['보호예수', '공시', '기대감']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2863,31 +2863,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>벡트로보틱스</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1829</v>
+        <v>10900</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.97%</t>
+          <t>'-27.33%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>75</v>
+        <v>382</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>181</v>
       </c>
       <c r="G27" t="n">
-        <v>44</v>
+        <v>646</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,47 +2895,47 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2575</v>
+        <v>15000</v>
       </c>
       <c r="K27" t="n">
-        <v>1960</v>
+        <v>12000</v>
       </c>
       <c r="L27" t="n">
-        <v>2005</v>
+        <v>12700</v>
       </c>
       <c r="M27" t="n">
-        <v>1805</v>
+        <v>9790</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>7202776610</v>
+        <v>109591159375</v>
       </c>
       <c r="P27" t="n">
-        <v>5700</v>
+        <v>12700</v>
       </c>
       <c r="Q27" t="n">
-        <v>1401</v>
+        <v>9790</v>
       </c>
       <c r="R27" t="n">
-        <v>73000</v>
+        <v>-41000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-216000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>연이은 하한가 기록. 투자자 불안감 고조 및 상장폐지 우려 제기.</t>
+          <t>상장 직후 급락 후 반등을 시도하는 종목으로, 높은 상승률 기대감과 함께 실제 매출 및 영업이익 수치가 제시되며 긍정적인 전망이 나타남.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['하한가', '유상증자', '상장폐지']</t>
+          <t>['상승률', '매출', '영업이익']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2943,91 +2943,91 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>457600</t>
+          <t>439270</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>벡트로보틱스</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10420</v>
+        <v>1821</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-30.53%</t>
+          <t>'-29.28%</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E28" t="n">
+        <v>76</v>
+      </c>
+      <c r="F28" t="n">
+        <v>42</v>
+      </c>
+      <c r="G28" t="n">
+        <v>47</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O28" t="n">
+        <v>7297693866</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R28" t="n">
+        <v>73000</v>
+      </c>
+      <c r="S28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>358</v>
-      </c>
-      <c r="F28" t="n">
-        <v>175</v>
-      </c>
-      <c r="G28" t="n">
-        <v>615</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M28" t="n">
-        <v>9790</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>104086434110</v>
-      </c>
-      <c r="P28" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>9790</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-41000</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-216000</v>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>상장 직후 급락 후 반등 시도. 당기순이익 및 매출액 호조. 실내골프대회 관련 긍정적 전망.</t>
+          <t>연이은 하한가 기록. 투자자 불안감 고조 및 상장폐지 우려 제기.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['당기순이익', '매출', '실내골프']</t>
+          <t>['하한가', '유상증자', '상장폐지']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>439270</t>
+          <t>457600</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261030_12.xlsx
+++ b/data/trending_integrated_20261030_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26450</v>
+        <v>25600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+193.89%</t>
+          <t>'+184.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>600</v>
+        <v>679</v>
       </c>
       <c r="F2" t="n">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="G2" t="n">
-        <v>679</v>
+        <v>740</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -601,7 +601,7 @@
         <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>27000</v>
+        <v>27100</v>
       </c>
       <c r="M2" t="n">
         <v>16450</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>534735890615</v>
+        <v>573171806215</v>
       </c>
       <c r="P2" t="n">
-        <v>27000</v>
+        <v>27100</v>
       </c>
       <c r="Q2" t="n">
         <v>16450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주의 높은 변동성과 급락에 대한 우려 속에서도 목표가 제시 및 상승 가능성에 대한 기대감이 일부 존재함. 엔비디아 관련 언급.</t>
+          <t>신규 상장 후 급등락 반복 속에서 목표가 제시 및 기대감이 일부 있으나, 변동성이 큰 신규주에 대한 주의 의견도 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장주', '목표가', '변동성']</t>
+          <t>['신규 상장', '목표가', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7150</v>
+        <v>7530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.58%</t>
+          <t>'+20.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
         <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>19004009375</v>
+        <v>21230487080</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>건설 경기 전환점 및 재료 기반 상승 기대. 유상 청약율 및 시장 상황 고려 필요.</t>
+          <t>단기 급등에 따른 차익 실현 가능성 언급, 재료 부각 기대감과 유상청약율, 주봉 분석 등 복합적 요소 고려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['건설 경기', '유상 청약', '재료']</t>
+          <t>['주봉 분석', '유상 청약율', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18980</v>
+        <v>19320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.99%</t>
+          <t>'+16.04%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>101379855520</v>
+        <v>103057339295</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자 관련 법 시행 수혜 및 보안 대장주로서의 기대감. 바이낸스, 빗썸 해킹 사태 반사이익 전망. 프로그램 매수세 유입.</t>
+          <t>양자암호통신 및 보안 이슈 부각과 함께 해킹 사태 수혜 기대감으로 주가 상승 전망이 우세하며, 기술력에 대한 긍정적 평가.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '수혜주']</t>
+          <t>['양자암호', '보안', '해킹 수혜']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2750</v>
+        <v>2765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.24%</t>
+          <t>'+12.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5" t="n">
         <v>0.79</v>
@@ -886,7 +886,7 @@
         <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>12033885513</v>
+        <v>12155037608</v>
       </c>
       <c r="P5" t="n">
         <v>3170</v>
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8580</v>
+        <v>8540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.43%</t>
+          <t>'+10.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
         <v>38</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>8006784560</v>
+        <v>8130617225</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12110</v>
+        <v>12180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.12%</t>
+          <t>'+8.75%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F7" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G7" t="n">
-        <v>776</v>
+        <v>793</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1070,7 +1070,7 @@
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>46556179580</v>
+        <v>47418041075</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1115,123 +1115,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15550</v>
+        <v>51600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.81%</t>
+          <t>'+5.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9</v>
+        <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>336</v>
+        <v>196</v>
       </c>
       <c r="H8" t="n">
-        <v>7.15</v>
+        <v>23.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14980</v>
+        <v>49100</v>
       </c>
       <c r="K8" t="n">
-        <v>14980</v>
+        <v>49450</v>
       </c>
       <c r="L8" t="n">
-        <v>16150</v>
+        <v>52000</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>48050</v>
       </c>
       <c r="N8" t="n">
-        <v>8.050000000000001</v>
+        <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>44306331845</v>
+        <v>53436456950</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>97900</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>30950</v>
       </c>
       <c r="R8" t="n">
-        <v>109000</v>
+        <v>-37000</v>
       </c>
       <c r="S8" t="n">
-        <v>168000</v>
+        <v>55000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
+          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 소부장 평균 PER 대비 저평가 분석.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
+          <t>['TC본더', '실적', '소부장']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29000</v>
+        <v>15650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.39%</t>
+          <t>'+4.47%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>288</v>
+        <v>350</v>
       </c>
       <c r="H9" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L9" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M9" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N9" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>111771814350</v>
+        <v>44888484515</v>
       </c>
       <c r="P9" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-45000</v>
+        <v>109000</v>
       </c>
       <c r="S9" t="n">
-        <v>95000</v>
+        <v>168000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50300</v>
+        <v>29150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.82</v>
+        <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>195</v>
+        <v>297</v>
       </c>
       <c r="H10" t="n">
-        <v>23.82</v>
+        <v>4.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>49100</v>
+        <v>28050</v>
       </c>
       <c r="K10" t="n">
-        <v>49450</v>
+        <v>27850</v>
       </c>
       <c r="L10" t="n">
-        <v>52000</v>
+        <v>30400</v>
       </c>
       <c r="M10" t="n">
-        <v>48050</v>
+        <v>27650</v>
       </c>
       <c r="N10" t="n">
-        <v>24.64</v>
+        <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>50268939900</v>
+        <v>113240972025</v>
       </c>
       <c r="P10" t="n">
-        <v>97900</v>
+        <v>50600</v>
       </c>
       <c r="Q10" t="n">
-        <v>30950</v>
+        <v>13210</v>
       </c>
       <c r="R10" t="n">
-        <v>-37000</v>
+        <v>-45000</v>
       </c>
       <c r="S10" t="n">
-        <v>55000</v>
+        <v>95000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 소부장 평균 PER 대비 저평가 분석.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['TC본더', '실적', '소부장']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15800</v>
+        <v>15860</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.51%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>40396895895</v>
+        <v>41585613245</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 조선주 강세 속에서 국내 조선주 기회론이 제기되었으나, 업황 둔화 및 승계 이슈에 대한 우려도 존재함. 리포트 쏟아짐.</t>
+          <t>미국 조선주 강세와 대비되는 국내 조선주 약세. 실적 서프라이즈 및 증권사 리포트 긍정 전망에도 불구하고 업황 둔화 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '호재', '업황']</t>
+          <t>['조선주', '실적 서프라이즈', '업황']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6590</v>
+        <v>3985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.05</v>
+        <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>1.43</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6640</v>
+        <v>4040</v>
       </c>
       <c r="K12" t="n">
-        <v>7210</v>
+        <v>3925</v>
       </c>
       <c r="L12" t="n">
-        <v>7500</v>
+        <v>4265</v>
       </c>
       <c r="M12" t="n">
-        <v>6490</v>
+        <v>3880</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>30521364695</v>
+        <v>76443505168</v>
       </c>
       <c r="P12" t="n">
-        <v>9820</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>4000</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-63000</v>
+        <v>-37000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['급등 기대', '외국인 매수', '개잡주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3950</v>
+        <v>7290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.23%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.77</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="H13" t="n">
-        <v>1.43</v>
+        <v>25.3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4040</v>
+        <v>7450</v>
       </c>
       <c r="K13" t="n">
-        <v>3925</v>
+        <v>7350</v>
       </c>
       <c r="L13" t="n">
-        <v>4265</v>
+        <v>7570</v>
       </c>
       <c r="M13" t="n">
-        <v>3880</v>
+        <v>7250</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>75602408845</v>
+        <v>8332363435</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>7010</v>
       </c>
       <c r="R13" t="n">
-        <v>-37000</v>
+        <v>95000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['급등 기대', '외국인 매수', '개잡주']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7270</v>
+        <v>61300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>191</v>
+        <v>293</v>
       </c>
       <c r="H14" t="n">
-        <v>25.3</v>
+        <v>41.76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7450</v>
+        <v>62800</v>
       </c>
       <c r="K14" t="n">
-        <v>7350</v>
+        <v>62300</v>
       </c>
       <c r="L14" t="n">
-        <v>7570</v>
+        <v>62800</v>
       </c>
       <c r="M14" t="n">
-        <v>7250</v>
+        <v>60700</v>
       </c>
       <c r="N14" t="n">
-        <v>25.32</v>
+        <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>8186060085</v>
+        <v>73129100200</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>7010</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>95000</v>
+        <v>117000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-38000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61200</v>
+        <v>6480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>283</v>
+        <v>70</v>
       </c>
       <c r="H15" t="n">
-        <v>41.76</v>
+        <v>0.85</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>62800</v>
+        <v>6640</v>
       </c>
       <c r="K15" t="n">
-        <v>62300</v>
+        <v>7210</v>
       </c>
       <c r="L15" t="n">
-        <v>62800</v>
+        <v>7500</v>
       </c>
       <c r="M15" t="n">
-        <v>60700</v>
+        <v>6470</v>
       </c>
       <c r="N15" t="n">
-        <v>41.55</v>
+        <v>0.9</v>
       </c>
       <c r="O15" t="n">
-        <v>71544465400</v>
+        <v>30721899545</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>9820</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>4000</v>
       </c>
       <c r="R15" t="n">
-        <v>117000</v>
+        <v>-63000</v>
       </c>
       <c r="S15" t="n">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8230</v>
+        <v>8350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.08%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="H16" t="n">
         <v>2.67</v>
@@ -1898,7 +1898,7 @@
         <v>2.66</v>
       </c>
       <c r="O16" t="n">
-        <v>27648065560</v>
+        <v>27848615540</v>
       </c>
       <c r="P16" t="n">
         <v>19270</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>서울반도체와의 비교 및 기술력에 대한 기대감. 환기 해소 후 기관 투자자 유입 가능성 및 실적 개선 전망.</t>
+          <t>서울반도체 대비 높은 영업이익 및 차세대 기술 기대감으로 긍정적 전망이 있으나, 환기 및 공매도 이슈로 인한 주가 제약.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '환기']</t>
+          <t>['영업이익', '차세대 기술', '환기']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54000</v>
+        <v>54100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.76%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F17" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G17" t="n">
-        <v>958</v>
+        <v>981</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>70140133950</v>
+        <v>72924383250</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 그러나 금융시장 무정부 상태 및 무능 정권 언급.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식에 긍정적 전망이 있으나, 정치적 요인으로 인한 시장 불안감도 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '원자로 수주', '실적']</t>
+          <t>['SMR 수주', '실적 개선', '뉴스케일파워']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>218500</v>
+        <v>11030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.82%</t>
+          <t>'-5.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>364</v>
       </c>
       <c r="F18" t="n">
-        <v>564</v>
+        <v>168</v>
       </c>
       <c r="G18" t="n">
-        <v>1487</v>
+        <v>1114</v>
       </c>
       <c r="H18" t="n">
-        <v>46.17</v>
+        <v>9.73</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>232000</v>
+        <v>11620</v>
       </c>
       <c r="K18" t="n">
-        <v>223500</v>
+        <v>11300</v>
       </c>
       <c r="L18" t="n">
-        <v>229500</v>
+        <v>11470</v>
       </c>
       <c r="M18" t="n">
-        <v>216500</v>
+        <v>10890</v>
       </c>
       <c r="N18" t="n">
-        <v>46.19</v>
+        <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2151855308500</v>
+        <v>48121504565</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>951000</v>
+        <v>-213000</v>
       </c>
       <c r="S18" t="n">
-        <v>-298000</v>
+        <v>-60000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>이재용 상속세 관련 정치적 언급과 함께 국장 전반의 하락세 및 삼성전자 주가에 대한 부정적 전망이 제기됨.</t>
+          <t>가덕도 공사비 증액 및 재건 사업 기대감. 공매도 금지 조치에 따른 영향 분석.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['가덕도', '공사비', '재건']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10940</v>
+        <v>219750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.85%</t>
+          <t>'-5.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>356</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>164</v>
+        <v>559</v>
       </c>
       <c r="G19" t="n">
-        <v>1104</v>
+        <v>1485</v>
       </c>
       <c r="H19" t="n">
-        <v>9.73</v>
+        <v>46.17</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>11620</v>
+        <v>232000</v>
       </c>
       <c r="K19" t="n">
-        <v>11300</v>
+        <v>223500</v>
       </c>
       <c r="L19" t="n">
-        <v>11470</v>
+        <v>229500</v>
       </c>
       <c r="M19" t="n">
-        <v>10890</v>
+        <v>216500</v>
       </c>
       <c r="N19" t="n">
-        <v>9.6</v>
+        <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>46952213880</v>
+        <v>2234327730000</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R19" t="n">
-        <v>-213000</v>
+        <v>951000</v>
       </c>
       <c r="S19" t="n">
-        <v>-60000</v>
+        <v>-298000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>가덕도 공사비 증액 및 재건 사업 기대감. 공매도 금지 조치에 따른 영향 분석.</t>
+          <t>이재용 상속세 이슈와 정치적 비판 속에서 주가 하락에 대한 부정적 심리가 지배적이며, 명확한 호재 부재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가덕도', '공사비', '재건']</t>
+          <t>['상속세', '정치', '주가 하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22000</v>
+        <v>172000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.78%</t>
+          <t>'-6.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>220</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>546</v>
+        <v>205</v>
       </c>
       <c r="H20" t="n">
-        <v>11.6</v>
+        <v>74.87</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>23600</v>
+        <v>183900</v>
       </c>
       <c r="K20" t="n">
-        <v>22650</v>
+        <v>176800</v>
       </c>
       <c r="L20" t="n">
-        <v>22700</v>
+        <v>179000</v>
       </c>
       <c r="M20" t="n">
-        <v>21100</v>
+        <v>168100</v>
       </c>
       <c r="N20" t="n">
-        <v>12.23</v>
+        <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>72162976275</v>
+        <v>514509477650</v>
       </c>
       <c r="P20" t="n">
-        <v>59300</v>
+        <v>243500</v>
       </c>
       <c r="Q20" t="n">
-        <v>21100</v>
+        <v>71000</v>
       </c>
       <c r="R20" t="n">
-        <v>-580000</v>
+        <v>-416000</v>
       </c>
       <c r="S20" t="n">
-        <v>-192000</v>
+        <v>-18000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 사업 관련 긍정적 뉴스(RE100, 물량 완판)에도 불구하고 급락세 지속.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 누르기', '태양광', 'RE100']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>170700</v>
+        <v>22000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.18%</t>
+          <t>'-6.78%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="G21" t="n">
-        <v>203</v>
+        <v>554</v>
       </c>
       <c r="H21" t="n">
-        <v>74.87</v>
+        <v>11.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,60 +2343,60 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>183900</v>
+        <v>23600</v>
       </c>
       <c r="K21" t="n">
-        <v>176800</v>
+        <v>22650</v>
       </c>
       <c r="L21" t="n">
-        <v>179000</v>
+        <v>22700</v>
       </c>
       <c r="M21" t="n">
-        <v>168100</v>
+        <v>21100</v>
       </c>
       <c r="N21" t="n">
-        <v>75</v>
+        <v>12.23</v>
       </c>
       <c r="O21" t="n">
-        <v>500157193250</v>
+        <v>73440813850</v>
       </c>
       <c r="P21" t="n">
-        <v>243500</v>
+        <v>59300</v>
       </c>
       <c r="Q21" t="n">
-        <v>71000</v>
+        <v>21100</v>
       </c>
       <c r="R21" t="n">
-        <v>-416000</v>
+        <v>-580000</v>
       </c>
       <c r="S21" t="n">
-        <v>-18000</v>
+        <v>-192000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 사업 관련 긍정적 뉴스(RE100, 물량 완판)에도 불구하고 급락세 지속.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['주가 누르기', '태양광', 'RE100']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1398000</v>
+        <v>1408000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.39%</t>
+          <t>'-7.73%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="G22" t="n">
-        <v>1300</v>
+        <v>1263</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>2632695966000</v>
+        <v>2757868361000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>증시 폭락 속에서 SK하이닉스 주가 하락에 대한 불만과 함께 정치적 책임론이 제기되었으며, 향후 주가에 대한 부정적 전망이 지배적임.</t>
+          <t>정부 비판 및 증시 불안감 속에서 SK하이닉스 주가 하락에 대한 부정적 의견이 다수이며, 실적 대비 저평가 논란.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['폭락', '정권', '증시']</t>
+          <t>['정부 비판', '증시 불안', '실적 저평가']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13710</v>
+        <v>13750</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.78%</t>
+          <t>'-8.52%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>108</v>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>40738179815</v>
+        <v>41417219270</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>광통신 섹터 내에서의 기대감. 루멘텀 홀딩스 관련 호재에도 불구하고 한국장 불신으로 인한 하락. 오후 반등 예상.</t>
+          <t>미국 광통신주 강세 및 기술력에 대한 기대감으로 매수 기회라는 의견이 있으나, 전반적인 시장 약세 및 정부 정책 불신으로 주가 상승에 제약.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '호재']</t>
+          <t>['광통신', '기술력', '시장 약세']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7100</v>
+        <v>7160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.13%</t>
+          <t>'-9.37%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>15177483110</v>
+        <v>15326659500</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116100</v>
+        <v>116400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.99%</t>
+          <t>'-15.77%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F25" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G25" t="n">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>137263452500</v>
+        <v>140687018200</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>급격한 주가 하락에 대한 의문과 함께 실적 호조에도 불구하고 하락하는 시장 상황에 대한 불만이 표출됨. 기관 및 외국인 매도세에 대한 비판도 제기됨.</t>
+          <t>실적 호조 기대에도 불구하고 급격한 주가 하락에 대한 불만과 음모론이 제기되며, 개인 투자자의 손실 우려.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '하락', '기관']</t>
+          <t>['실적 호조', '급락', '개인 투자자']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13130</v>
+        <v>13450</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-22.76%</t>
+          <t>'-20.88%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F26" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G26" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>32166881345</v>
+        <v>33583377320</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10900</v>
+        <v>10690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-27.33%</t>
+          <t>'-28.73%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="F27" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G27" t="n">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="H27" t="n">
         <v>3.05</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>109591159375</v>
+        <v>112723132985</v>
       </c>
       <c r="P27" t="n">
         <v>12700</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>상장 직후 급락 후 반등을 시도하는 종목으로, 높은 상승률 기대감과 함께 실제 매출 및 영업이익 수치가 제시되며 긍정적인 전망이 나타남.</t>
+          <t>상장 직후 하한가 기록 후 반등 기대감이 있으나, 실적 대비 주가 수준 및 수급에 대한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상승률', '매출', '영업이익']</t>
+          <t>['상장 직후', '실적', '수급']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1821</v>
+        <v>1805</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-29.28%</t>
+          <t>'-29.90%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1.45</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F28" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G28" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
         <v>4.8</v>
@@ -3002,7 +3002,7 @@
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>7297693866</v>
+        <v>7393642593</v>
       </c>
       <c r="P28" t="n">
         <v>5700</v>
@@ -3018,16 +3018,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>연이은 하한가 기록. 투자자 불안감 고조 및 상장폐지 우려 제기.</t>
+          <t>유증 납입 지연 및 하한가 기록 등 악재가 겹치며 상장폐지 우려와 투자자 손실에 대한 경고가 지배적.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['하한가', '유상증자', '상장폐지']</t>
+          <t>['유증 납입 지연', '하한가', '상폐 우려']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">

--- a/data/trending_integrated_20261030_12.xlsx
+++ b/data/trending_integrated_20261030_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25600</v>
+        <v>23600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+184.44%</t>
+          <t>'+162.22%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>679</v>
+        <v>724</v>
       </c>
       <c r="F2" t="n">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="G2" t="n">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>573171806215</v>
+        <v>604467149390</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7530</v>
+        <v>7650</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.67%</t>
+          <t>'+22.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>6700</v>
       </c>
       <c r="L3" t="n">
-        <v>7670</v>
+        <v>7750</v>
       </c>
       <c r="M3" t="n">
         <v>6330</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>21230487080</v>
+        <v>24497884240</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>단기 급등에 따른 차익 실현 가능성 언급, 재료 부각 기대감과 유상청약율, 주봉 분석 등 복합적 요소 고려.</t>
+          <t>가짜 상승에 대한 경고와 함께 건설업 부흥 기대감 표출. 유상청약율 및 재료에 대한 의구심 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주봉 분석', '유상 청약율', '재료']</t>
+          <t>['건설', '유상청약율', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19320</v>
+        <v>19230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.04%</t>
+          <t>'+15.50%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>103057339295</v>
+        <v>104085849735</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자암호통신 및 보안 이슈 부각과 함께 해킹 사태 수혜 기대감으로 주가 상승 전망이 우세하며, 기술력에 대한 긍정적 평가.</t>
+          <t>11월 양자관련법 시행 및 정부 정책 수혜 기대. 보안 대장주로서 해킹 사태 수혜 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '해킹 수혜']</t>
+          <t>['양자보안', '수혜주', '해킹']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2765</v>
+        <v>2750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.86%</t>
+          <t>'+12.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
         <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
         <v>0.79</v>
@@ -886,7 +886,7 @@
         <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>12155037608</v>
+        <v>12262206042</v>
       </c>
       <c r="P5" t="n">
         <v>3170</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8540</v>
+        <v>8570</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.91%</t>
+          <t>'+11.30%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H6" t="n">
         <v>13.29</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>8130617225</v>
+        <v>8205006165</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12180</v>
+        <v>12300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.75%</t>
+          <t>'+9.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F7" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G7" t="n">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1070,7 +1070,7 @@
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>47418041075</v>
+        <v>49135883485</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>희토류 없는 백색 LED 세계 최초 개발 및 언론 보도. 100억 달러 시장 석권 기대감. 주당 10만원 이상 목표.</t>
+          <t>희토류 없는 백색 LED 개발 등 기술력 강조. 세계 1위 기업으로서 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '시장 석권']</t>
+          <t>['백색LED', '희토류', '기술개발']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51600</v>
+        <v>15690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.09%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.82</v>
+        <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>196</v>
+        <v>356</v>
       </c>
       <c r="H8" t="n">
-        <v>23.82</v>
+        <v>7.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49100</v>
+        <v>14980</v>
       </c>
       <c r="K8" t="n">
-        <v>49450</v>
+        <v>14980</v>
       </c>
       <c r="L8" t="n">
-        <v>52000</v>
+        <v>16150</v>
       </c>
       <c r="M8" t="n">
-        <v>48050</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>24.64</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>53436456950</v>
+        <v>45476106025</v>
       </c>
       <c r="P8" t="n">
-        <v>97900</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>30950</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>-37000</v>
+        <v>109000</v>
       </c>
       <c r="S8" t="n">
-        <v>55000</v>
+        <v>168000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 소부장 평균 PER 대비 저평가 분석.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['TC본더', '실적', '소부장']</t>
+          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15650</v>
+        <v>51300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.47%</t>
+          <t>'+4.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>350</v>
+        <v>205</v>
       </c>
       <c r="H9" t="n">
-        <v>7.15</v>
+        <v>23.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>49100</v>
       </c>
       <c r="K9" t="n">
-        <v>14980</v>
+        <v>49450</v>
       </c>
       <c r="L9" t="n">
-        <v>16150</v>
+        <v>52000</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>48050</v>
       </c>
       <c r="N9" t="n">
-        <v>8.050000000000001</v>
+        <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>44888484515</v>
+        <v>56188040850</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>97900</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>30950</v>
       </c>
       <c r="R9" t="n">
-        <v>109000</v>
+        <v>-37000</v>
       </c>
       <c r="S9" t="n">
-        <v>168000</v>
+        <v>55000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
+          <t>최대 실적 발표에도 불구하고 주가 부진에 대한 아쉬움 표출. TC본더 매출 본격화, HBM 시대 도래 기대감. 공매도 및 소부장 밸류에이션 비교.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
+          <t>['실적', 'TC본더', 'HBM']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29150</v>
+        <v>29300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H10" t="n">
         <v>4.69</v>
@@ -1346,7 +1346,7 @@
         <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>113240972025</v>
+        <v>114110124100</v>
       </c>
       <c r="P10" t="n">
         <v>50600</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15860</v>
+        <v>15830</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.89%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>41585613245</v>
+        <v>42703017585</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 조선주 강세와 대비되는 국내 조선주 약세. 실적 서프라이즈 및 증권사 리포트 긍정 전망에도 불구하고 업황 둔화 우려.</t>
+          <t>미국 조선주 상승 속 국내 조선주 기회 기대. 3분기 실적 서프라이즈 및 증권사 리포트 긍정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '실적 서프라이즈', '업황']</t>
+          <t>['실적 서프라이즈', '조선주', '증권사 리포트']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3985</v>
+        <v>3990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>76443505168</v>
+        <v>76806600725</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
+          <t>긍정적 분위기 속 급등 기대감 있으나, 개잡주 및 작전 세력 의혹 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['급등 기대', '외국인 매수', '개잡주']</t>
+          <t>['급등 기대', '작전 의혹', '개잡주']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7290</v>
+        <v>61700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="H13" t="n">
-        <v>25.3</v>
+        <v>41.76</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7450</v>
+        <v>62800</v>
       </c>
       <c r="K13" t="n">
-        <v>7350</v>
+        <v>62300</v>
       </c>
       <c r="L13" t="n">
-        <v>7570</v>
+        <v>62800</v>
       </c>
       <c r="M13" t="n">
-        <v>7250</v>
+        <v>60700</v>
       </c>
       <c r="N13" t="n">
-        <v>25.32</v>
+        <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>8332363435</v>
+        <v>75435844800</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>7010</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>95000</v>
+        <v>117000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>-38000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61300</v>
+        <v>6500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.11%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>293</v>
+        <v>68</v>
       </c>
       <c r="H14" t="n">
-        <v>41.76</v>
+        <v>0.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62800</v>
+        <v>6640</v>
       </c>
       <c r="K14" t="n">
-        <v>62300</v>
+        <v>7210</v>
       </c>
       <c r="L14" t="n">
-        <v>62800</v>
+        <v>7500</v>
       </c>
       <c r="M14" t="n">
-        <v>60700</v>
+        <v>6470</v>
       </c>
       <c r="N14" t="n">
-        <v>41.55</v>
+        <v>0.9</v>
       </c>
       <c r="O14" t="n">
-        <v>73129100200</v>
+        <v>30852125565</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>9820</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>4000</v>
       </c>
       <c r="R14" t="n">
-        <v>117000</v>
+        <v>-63000</v>
       </c>
       <c r="S14" t="n">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6480</v>
+        <v>7290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="H15" t="n">
-        <v>0.85</v>
+        <v>25.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6640</v>
+        <v>7450</v>
       </c>
       <c r="K15" t="n">
-        <v>7210</v>
+        <v>7350</v>
       </c>
       <c r="L15" t="n">
-        <v>7500</v>
+        <v>7570</v>
       </c>
       <c r="M15" t="n">
-        <v>6470</v>
+        <v>7250</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9</v>
+        <v>25.32</v>
       </c>
       <c r="O15" t="n">
-        <v>30721899545</v>
+        <v>8435139150</v>
       </c>
       <c r="P15" t="n">
-        <v>9820</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>4000</v>
+        <v>7010</v>
       </c>
       <c r="R15" t="n">
-        <v>-63000</v>
+        <v>95000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8350</v>
+        <v>8380</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
         <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H16" t="n">
         <v>2.67</v>
@@ -1898,7 +1898,7 @@
         <v>2.66</v>
       </c>
       <c r="O16" t="n">
-        <v>27848615540</v>
+        <v>28127138160</v>
       </c>
       <c r="P16" t="n">
         <v>19270</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>서울반도체 대비 높은 영업이익 및 차세대 기술 기대감으로 긍정적 전망이 있으나, 환기 및 공매도 이슈로 인한 주가 제약.</t>
+          <t>서울바이오시스의 서울반도체 대비 높은 영업이익 및 기술력 언급. 환기 해제 기대감과 기관 투자 유입 가능성 전망. 제2의 한미반도체, 초전도체, 광반도체 비유.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['영업이익', '차세대 기술', '환기']</t>
+          <t>['영업이익', '환기', '광반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54100</v>
+        <v>54200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F17" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G17" t="n">
-        <v>981</v>
+        <v>1005</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>72924383250</v>
+        <v>73842978400</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식에 긍정적 전망이 있으나, 정치적 요인으로 인한 시장 불안감도 존재.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 확인. 체코 원전 수주 실패 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11030</v>
+        <v>11050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.08%</t>
+          <t>'-4.91%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F18" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G18" t="n">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2082,7 +2082,7 @@
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>48121504565</v>
+        <v>48657737970</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>219750</v>
+        <v>220250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.28%</t>
+          <t>'-5.06%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G19" t="n">
-        <v>1485</v>
+        <v>1449</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>2234327730000</v>
+        <v>2285778097250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>이재용 상속세 이슈와 정치적 비판 속에서 주가 하락에 대한 부정적 심리가 지배적이며, 명확한 호재 부재.</t>
+          <t>이재용 상속세 관련 부정적 언급 다수, 주가 하락 원인으로 지목. 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상속세', '정치', '주가 하락']</t>
+          <t>['상속세', '주가 하락', '정부 정책']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>172000</v>
+        <v>173100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.47%</t>
+          <t>'-5.87%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>514509477650</v>
+        <v>525155783300</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22000</v>
+        <v>22100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.78%</t>
+          <t>'-6.36%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.63</v>
       </c>
       <c r="E21" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F21" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G21" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H21" t="n">
         <v>11.6</v>
@@ -2358,7 +2358,7 @@
         <v>12.23</v>
       </c>
       <c r="O21" t="n">
-        <v>73440813850</v>
+        <v>74245903500</v>
       </c>
       <c r="P21" t="n">
         <v>59300</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1408000</v>
+        <v>1413000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.73%</t>
+          <t>'-7.40%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G22" t="n">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>2757868361000</v>
+        <v>2842665044000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정부 비판 및 증시 불안감 속에서 SK하이닉스 주가 하락에 대한 부정적 의견이 다수이며, 실적 대비 저평가 논란.</t>
+          <t>정치권 비판과 함께 주가 하락에 대한 불만 고조. 엔비디아 회복세 기대감 있으나 하락세 우려 공존.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['정부 비판', '증시 불안', '실적 저평가']</t>
+          <t>['정치 비판', '주가 하락', '엔비디아']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13750</v>
+        <v>13770</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.52%</t>
+          <t>'-8.38%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>41417219270</v>
+        <v>41963942920</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 및 기술력에 대한 기대감으로 매수 기회라는 의견이 있으나, 전반적인 시장 약세 및 정부 정책 불신으로 주가 상승에 제약.</t>
+          <t>상승 기대감과 정부 정책에 대한 불신 혼재. 특허 및 루멘텀 관련 언급. 조정 시 매수 기회로 인식.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '기술력', '시장 약세']</t>
+          <t>['광통신', '특허', '정부']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7160</v>
+        <v>7120</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.37%</t>
+          <t>'-9.87%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>15326659500</v>
+        <v>15543205850</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116400</v>
+        <v>116900</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.77%</t>
+          <t>'-15.41%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F25" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>140687018200</v>
+        <v>143531929850</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 호조 기대에도 불구하고 급격한 주가 하락에 대한 불만과 음모론이 제기되며, 개인 투자자의 손실 우려.</t>
+          <t>대폭 하락에 대한 불만과 실적 대비 주가 부진 지적. 방송 추천 내용 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적 호조', '급락', '개인 투자자']</t>
+          <t>['실적', '주가 부진', '하락']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13450</v>
+        <v>13760</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-20.88%</t>
+          <t>'-19.06%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F26" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G26" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>33583377320</v>
+        <v>35052972875</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 및 급락하는 시장 상황 속에서 주가 하락에 대한 불만이 제기되었으나, 마이크론 퀄테스트 통과 및 장비 수주 공시 기대감이 언급됨.</t>
+          <t>보호예수 물량 및 급락에 대한 우려 표출. 마이크론 퀄 테스트 통과와 장비 수주 공시 기대감 존재. 저점 매수 및 기술적 반등 가능성 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '공시', '기대감']</t>
+          <t>['보호예수', '장비수주', '퀄테스트']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10690</v>
+        <v>11100</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.73%</t>
+          <t>'-26.00%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="F27" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G27" t="n">
-        <v>642</v>
+        <v>672</v>
       </c>
       <c r="H27" t="n">
         <v>3.05</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>112723132985</v>
+        <v>121090838125</v>
       </c>
       <c r="P27" t="n">
         <v>12700</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>상장 직후 하한가 기록 후 반등 기대감이 있으나, 실적 대비 주가 수준 및 수급에 대한 불확실성 존재.</t>
+          <t>상장 직후 하락세 속에서도 긍정적 전망 존재. 매출 및 영업이익 지표 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상장 직후', '실적', '수급']</t>
+          <t>['상장', '매출', '영업이익']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2970,13 +2970,13 @@
         <v>1.45</v>
       </c>
       <c r="E28" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F28" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="H28" t="n">
         <v>4.8</v>
@@ -3002,7 +3002,7 @@
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>7393642593</v>
+        <v>7443578857</v>
       </c>
       <c r="P28" t="n">
         <v>5700</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>유증 납입 지연 및 하한가 기록 등 악재가 겹치며 상장폐지 우려와 투자자 손실에 대한 경고가 지배적.</t>
+          <t>하한가 근처 주가 흐름에 대한 부정적 전망 및 상폐 우려. 납입 공시 및 3자 배정 관련 논의.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['유증 납입 지연', '하한가', '상폐 우려']</t>
+          <t>['하한가', '상폐 우려', '3자배정']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_12.xlsx
+++ b/data/trending_integrated_20261030_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23600</v>
+        <v>23350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+162.22%</t>
+          <t>'+159.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>724</v>
+        <v>752</v>
       </c>
       <c r="F2" t="n">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="G2" t="n">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>604467149390</v>
+        <v>634189875565</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장 후 급등락 반복 속에서 목표가 제시 및 기대감이 일부 있으나, 변동성이 큰 신규주에 대한 주의 의견도 공존.</t>
+          <t>단기 급등 후 변동성이 큰 신규 상장주에 대한 언급. 단타 및 목표가 관련 내용.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장', '목표가', '변동성']</t>
+          <t>['단타', '신규상장주', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7650</v>
+        <v>7630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.60%</t>
+          <t>'+22.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>6700</v>
       </c>
       <c r="L3" t="n">
-        <v>7750</v>
+        <v>7880</v>
       </c>
       <c r="M3" t="n">
         <v>6330</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>24497884240</v>
+        <v>27494355495</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19230</v>
+        <v>19330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.50%</t>
+          <t>'+16.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>104085849735</v>
+        <v>105936991515</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2750</v>
+        <v>2790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.24%</t>
+          <t>'+13.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>12262206042</v>
+        <v>12432735727</v>
       </c>
       <c r="P5" t="n">
         <v>3170</v>
@@ -946,13 +946,13 @@
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
         <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H6" t="n">
         <v>13.29</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>8205006165</v>
+        <v>8279351045</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12300</v>
+        <v>12320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.82%</t>
+          <t>'+10.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F7" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G7" t="n">
-        <v>805</v>
+        <v>843</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1070,7 +1070,7 @@
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>49135883485</v>
+        <v>50113377610</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>희토류 없는 백색 LED 개발 등 기술력 강조. 세계 1위 기업으로서 주가 상승 전망.</t>
+          <t>희토류 없는 백색 LED 기술 개발에 따른 높은 성장 기대감. 세계 1위 기업으로서의 위상 및 향후 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '기술개발']</t>
+          <t>['백색LED', '기술개발', '성장전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15690</v>
+        <v>15710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+4.87%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H8" t="n">
         <v>7.15</v>
@@ -1162,7 +1162,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>45476106025</v>
+        <v>45854341035</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1207,79 +1207,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51300</v>
+        <v>29050</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.48%</t>
+          <t>'+3.57%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.82</v>
+        <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>23.82</v>
+        <v>4.69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>49100</v>
+        <v>28050</v>
       </c>
       <c r="K9" t="n">
-        <v>49450</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>48050</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24.64</v>
+        <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>56188040850</v>
+        <v>115175000000</v>
       </c>
       <c r="P9" t="n">
-        <v>97900</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>30950</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-37000</v>
+        <v>-45000</v>
       </c>
       <c r="S9" t="n">
-        <v>55000</v>
+        <v>95000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>최대 실적 발표에도 불구하고 주가 부진에 대한 아쉬움 표출. TC본더 매출 본격화, HBM 시대 도래 기대감. 공매도 및 소부장 밸류에이션 비교.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', 'HBM']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,91 +1287,91 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29300</v>
+        <v>50500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+2.85%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.36</v>
+        <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G10" t="n">
-        <v>301</v>
+        <v>216</v>
       </c>
       <c r="H10" t="n">
-        <v>4.69</v>
+        <v>23.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>28050</v>
+        <v>49100</v>
       </c>
       <c r="K10" t="n">
-        <v>27850</v>
+        <v>49450</v>
       </c>
       <c r="L10" t="n">
-        <v>30400</v>
+        <v>52000</v>
       </c>
       <c r="M10" t="n">
-        <v>27650</v>
+        <v>48050</v>
       </c>
       <c r="N10" t="n">
-        <v>5.05</v>
+        <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>114110124100</v>
+        <v>57431366850</v>
       </c>
       <c r="P10" t="n">
-        <v>50600</v>
+        <v>97900</v>
       </c>
       <c r="Q10" t="n">
-        <v>13210</v>
+        <v>30950</v>
       </c>
       <c r="R10" t="n">
-        <v>-45000</v>
+        <v>-37000</v>
       </c>
       <c r="S10" t="n">
-        <v>95000</v>
+        <v>55000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>견조한 실적 발표에도 불구하고 지수 영향으로 인한 주가 부진. TC본더 매출 본격화 및 실적 개선 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['실적개선', 'TC본더', '주가전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15830</v>
+        <v>15800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.51%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
         <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>42703017585</v>
+        <v>43608827735</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3990</v>
+        <v>4005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-0.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
         <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>76806600725</v>
+        <v>77279483380</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>긍정적 분위기 속 급등 기대감 있으나, 개잡주 및 작전 세력 의혹 존재.</t>
+          <t>국내 증시 전반의 하락 속에서도 상대적인 선방에 대한 기대감. 외국인 및 프로그램 매수세 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['급등 기대', '작전 의혹', '개잡주']</t>
+          <t>['상승기대', '외국인매수', '국내증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1596,7 +1596,7 @@
         <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H13" t="n">
         <v>41.76</v>
@@ -1622,7 +1622,7 @@
         <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>75435844800</v>
+        <v>76759711650</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1667,70 +1667,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6500</v>
+        <v>7310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.11%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
-        <v>68</v>
+        <v>212</v>
       </c>
       <c r="H14" t="n">
-        <v>0.85</v>
+        <v>25.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6640</v>
+        <v>7450</v>
       </c>
       <c r="K14" t="n">
-        <v>7210</v>
+        <v>7350</v>
       </c>
       <c r="L14" t="n">
-        <v>7500</v>
+        <v>7570</v>
       </c>
       <c r="M14" t="n">
-        <v>6470</v>
+        <v>7250</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>30852125565</v>
+        <v>8650258190</v>
       </c>
       <c r="P14" t="n">
-        <v>9820</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>4000</v>
+        <v>7010</v>
       </c>
       <c r="R14" t="n">
-        <v>-63000</v>
+        <v>95000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7290</v>
+        <v>8400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="H15" t="n">
-        <v>25.3</v>
+        <v>2.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7450</v>
+        <v>8580</v>
       </c>
       <c r="K15" t="n">
-        <v>7350</v>
+        <v>11090</v>
       </c>
       <c r="L15" t="n">
-        <v>7570</v>
+        <v>11150</v>
       </c>
       <c r="M15" t="n">
-        <v>7250</v>
+        <v>8110</v>
       </c>
       <c r="N15" t="n">
-        <v>25.32</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>8435139150</v>
+        <v>28459579240</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>19270</v>
       </c>
       <c r="Q15" t="n">
-        <v>7010</v>
+        <v>2135</v>
       </c>
       <c r="R15" t="n">
-        <v>95000</v>
+        <v>-363000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>-2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>높은 기술력을 바탕으로 한 제2의 한미반도체 성장 기대감. 광통신 사업 진출 및 매출 증대 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['기술력', '성장기대', '광통신']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,43 +1839,43 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8380</v>
+        <v>6470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.33%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="H16" t="n">
-        <v>2.67</v>
+        <v>0.85</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8580</v>
+        <v>6640</v>
       </c>
       <c r="K16" t="n">
-        <v>11090</v>
+        <v>7210</v>
       </c>
       <c r="L16" t="n">
-        <v>11150</v>
+        <v>7500</v>
       </c>
       <c r="M16" t="n">
-        <v>8110</v>
+        <v>6450</v>
       </c>
       <c r="N16" t="n">
-        <v>2.66</v>
+        <v>0.9</v>
       </c>
       <c r="O16" t="n">
-        <v>28127138160</v>
+        <v>30961885045</v>
       </c>
       <c r="P16" t="n">
-        <v>19270</v>
+        <v>9820</v>
       </c>
       <c r="Q16" t="n">
-        <v>2135</v>
+        <v>4000</v>
       </c>
       <c r="R16" t="n">
-        <v>-363000</v>
+        <v>-63000</v>
       </c>
       <c r="S16" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>서울바이오시스의 서울반도체 대비 높은 영업이익 및 기술력 언급. 환기 해제 기대감과 기관 투자 유입 가능성 전망. 제2의 한미반도체, 초전도체, 광반도체 비유.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['영업이익', '환기', '광반도체']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54200</v>
+        <v>54100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="F17" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="G17" t="n">
-        <v>1005</v>
+        <v>1021</v>
       </c>
       <c r="H17" t="n">
         <v>22.14</v>
@@ -1990,7 +1990,7 @@
         <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>73842978400</v>
+        <v>74644913550</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2050,13 +2050,13 @@
         <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F18" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G18" t="n">
-        <v>1126</v>
+        <v>1147</v>
       </c>
       <c r="H18" t="n">
         <v>9.73</v>
@@ -2082,7 +2082,7 @@
         <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>48657737970</v>
+        <v>49280938285</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>220250</v>
+        <v>220500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.06%</t>
+          <t>'-4.96%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="G19" t="n">
-        <v>1449</v>
+        <v>1411</v>
       </c>
       <c r="H19" t="n">
         <v>46.17</v>
@@ -2174,7 +2174,7 @@
         <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>2285778097250</v>
+        <v>2330383014750</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>이재용 상속세 관련 부정적 언급 다수, 주가 하락 원인으로 지목. 정부 정책 비판.</t>
+          <t>이재용 상속세 관련 부정적 여론 및 정치적 이슈로 인한 주가 하락 우려. 시장 전반에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상속세', '주가 하락', '정부 정책']</t>
+          <t>['상속세', '정치이슈', '주가하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>173100</v>
+        <v>172900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.87%</t>
+          <t>'-5.98%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>525155783300</v>
+        <v>534971825350</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22100</v>
+        <v>22050</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.36%</t>
+          <t>'-6.57%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.63</v>
       </c>
       <c r="E21" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F21" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G21" t="n">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="H21" t="n">
         <v>11.6</v>
@@ -2358,7 +2358,7 @@
         <v>12.23</v>
       </c>
       <c r="O21" t="n">
-        <v>74245903500</v>
+        <v>75016662550</v>
       </c>
       <c r="P21" t="n">
         <v>59300</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1413000</v>
+        <v>1414000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.40%</t>
+          <t>'-7.34%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="G22" t="n">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>2842665044000</v>
+        <v>2900364888500</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치권 비판과 함께 주가 하락에 대한 불만 고조. 엔비디아 회복세 기대감 있으나 하락세 우려 공존.</t>
+          <t>정치적 불만과 시장 하락 속에서 SK하이닉스 주가에 대한 불만 표출. 연기금 운용 및 정부 정책에 대한 비판.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['정치 비판', '주가 하락', '엔비디아']</t>
+          <t>['정부정책', '연기금', '주가하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13770</v>
+        <v>13790</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.38%</t>
+          <t>'-8.25%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>41963942920</v>
+        <v>42724389555</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7120</v>
+        <v>7100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.87%</t>
+          <t>'-10.13%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>15543205850</v>
+        <v>15760399235</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2679,83 +2679,83 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116900</v>
+        <v>14950</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.41%</t>
+          <t>'-12.06%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.26</v>
+        <v>0.01</v>
       </c>
       <c r="E25" t="n">
-        <v>160</v>
+        <v>209</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G25" t="n">
-        <v>414</v>
+        <v>188</v>
       </c>
       <c r="H25" t="n">
-        <v>14.2</v>
+        <v>0.66</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>138200</v>
+        <v>17000</v>
       </c>
       <c r="K25" t="n">
-        <v>132600</v>
+        <v>14000</v>
       </c>
       <c r="L25" t="n">
-        <v>132900</v>
+        <v>15280</v>
       </c>
       <c r="M25" t="n">
-        <v>114300</v>
+        <v>12930</v>
       </c>
       <c r="N25" t="n">
-        <v>14.46</v>
+        <v>0.65</v>
       </c>
       <c r="O25" t="n">
-        <v>143531929850</v>
+        <v>48717579625</v>
       </c>
       <c r="P25" t="n">
-        <v>198000</v>
+        <v>28800</v>
       </c>
       <c r="Q25" t="n">
-        <v>36450</v>
+        <v>11550</v>
       </c>
       <c r="R25" t="n">
-        <v>-312000</v>
+        <v>-24000</v>
       </c>
       <c r="S25" t="n">
-        <v>-29000</v>
+        <v>-170000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대폭 하락에 대한 불만과 실적 대비 주가 부진 지적. 방송 추천 내용 언급.</t>
+          <t>보호예수 물량 해제 및 주가 하락에 대한 부정적 시각. 장비 수주 공시 필요성 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '주가 부진', '하락']</t>
+          <t>['보호예수', '주가하락', '장비수주']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,90 +2764,90 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13760</v>
+        <v>116100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-19.06%</t>
+          <t>'-15.99%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="E26" t="n">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>176</v>
+        <v>412</v>
       </c>
       <c r="H26" t="n">
-        <v>0.66</v>
+        <v>14.2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>17000</v>
+        <v>138200</v>
       </c>
       <c r="K26" t="n">
-        <v>14000</v>
+        <v>132600</v>
       </c>
       <c r="L26" t="n">
-        <v>14900</v>
+        <v>132900</v>
       </c>
       <c r="M26" t="n">
-        <v>12930</v>
+        <v>114300</v>
       </c>
       <c r="N26" t="n">
-        <v>0.65</v>
+        <v>14.46</v>
       </c>
       <c r="O26" t="n">
-        <v>35052972875</v>
+        <v>146674090250</v>
       </c>
       <c r="P26" t="n">
-        <v>28800</v>
+        <v>198000</v>
       </c>
       <c r="Q26" t="n">
-        <v>11550</v>
+        <v>36450</v>
       </c>
       <c r="R26" t="n">
-        <v>-24000</v>
+        <v>-312000</v>
       </c>
       <c r="S26" t="n">
-        <v>-170000</v>
+        <v>-29000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 및 급락에 대한 우려 표출. 마이크론 퀄 테스트 통과와 장비 수주 공시 기대감 존재. 저점 매수 및 기술적 반등 가능성 언급.</t>
+          <t>실적 호조 전망에도 불구하고 급락한 대덕전자에 대한 투자자들의 혼란과 불신이 나타나고 있음. 일부는 저가 매수를 고려하나, 급락 원인에 대한 의문과 불안감이 공존함.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '장비수주', '퀄테스트']</t>
+          <t>['실적', '급락', '투자심리']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>353200</t>
         </is>
       </c>
     </row>
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11100</v>
+        <v>10670</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-26.00%</t>
+          <t>'-28.87%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="F27" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G27" t="n">
-        <v>672</v>
+        <v>737</v>
       </c>
       <c r="H27" t="n">
         <v>3.05</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>121090838125</v>
+        <v>125271986370</v>
       </c>
       <c r="P27" t="n">
         <v>12700</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>상장 직후 하락세 속에서도 긍정적 전망 존재. 매출 및 영업이익 지표 언급.</t>
+          <t>신규 상장주의 높은 영업이익 대비 낮은 주가에 대한 긍정적 전망. 인텔리빅스와의 비교 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상장', '매출', '영업이익']</t>
+          <t>['영업이익', '신규상장주', '가치평가']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2976,7 +2976,7 @@
         <v>47</v>
       </c>
       <c r="G28" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H28" t="n">
         <v>4.8</v>
@@ -3002,7 +3002,7 @@
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>7443578857</v>
+        <v>7451964887</v>
       </c>
       <c r="P28" t="n">
         <v>5700</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>하한가 근처 주가 흐름에 대한 부정적 전망 및 상폐 우려. 납입 공시 및 3자 배정 관련 논의.</t>
+          <t>납입 이슈 및 하한가 행진에 대한 부정적 전망. 상폐 가능성 및 투자 주의 언급.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['하한가', '상폐 우려', '3자배정']</t>
+          <t>['납입이슈', '하한가', '상폐가능성']</t>
         </is>
       </c>
       <c r="X28" t="n">
